--- a/data/Patient_ground_truth.xlsx
+++ b/data/Patient_ground_truth.xlsx
@@ -5,29 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Clinicum Digitale\Tumor Documentation Webtool\Scripts\main_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Clinicum Digitale\Tumor Documentation Webtool\Scripts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CBE667-CEB7-4AFA-B369-A94EAA1E7442}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD2E1F-8A86-4BFA-A8D6-8246E2B33847}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="42696" windowHeight="15804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="eval_ground_truth" sheetId="1" r:id="rId1"/>
+    <sheet name="Patient_ground_truth" sheetId="1" r:id="rId1"/>
     <sheet name="method_notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eval_ground_truth!$A$2:$AD$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Patient_ground_truth!$A$1:$AD$11</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="211">
-  <si>
-    <t>Document-derived ground truth for synthetic oncology PDFs</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="210">
   <si>
     <t>real_id</t>
   </si>
@@ -663,19 +660,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -688,17 +679,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -727,12 +713,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1040,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1068,1057 +1052,1020 @@
     <col min="29" max="29" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>30</v>
+      <c r="D2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="A3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="D3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="3">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="5" t="s">
+      <c r="R3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD3" s="5" t="s">
-        <v>55</v>
+      <c r="U3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="5" t="s">
+      <c r="D4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>74</v>
+      <c r="R4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="A5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="O5" s="5">
+      <c r="N5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O5" s="3">
         <v>1</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="S5" s="5" t="s">
+      <c r="P5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>90</v>
+      <c r="U5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="A6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="D6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="N6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R6" s="5" t="s">
+      <c r="Q6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA6" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC6" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AD6" s="5" t="s">
-        <v>110</v>
+      <c r="T6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="A7" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="D7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="L7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="M7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="N7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5" t="s">
+      <c r="Q7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="V7" s="5" t="s">
+      <c r="R7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="W7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="W7" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="X7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y7" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA7" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB7" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>126</v>
+      <c r="X7" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="A8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="3">
         <v>1</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="D8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="O8" s="5">
+      <c r="N8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O8" s="3">
         <v>1</v>
       </c>
-      <c r="P8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="P8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y8" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="Z8" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB8" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC8" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="AD8" s="5" t="s">
-        <v>142</v>
+      <c r="T8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="A9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="D9" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="O9" s="5">
+      <c r="M9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="O9" s="3">
         <v>1</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="W9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y9" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z9" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA9" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB9" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC9" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD9" s="5" t="s">
-        <v>158</v>
+      <c r="R9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="A10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="3">
         <v>1</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="D10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="O10" s="5">
+      <c r="N10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O10" s="3">
         <v>1</v>
       </c>
-      <c r="P10" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB10" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC10" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="AD10" s="5" t="s">
-        <v>176</v>
+      <c r="P10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="A11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="D11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="L11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="M11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="O11" s="5">
+      <c r="N11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="O11" s="3">
         <v>1</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="P11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA11" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB11" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC11" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD11" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1</v>
-      </c>
-      <c r="P12" s="5" t="s">
+      <c r="R11" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R12" s="5" t="s">
+      <c r="S11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="S12" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U12" s="5" t="s">
+      <c r="V11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="V12" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="W12" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="X12" s="5" t="s">
+      <c r="Y11" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Z11" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="Z12" s="5" t="s">
+      <c r="AA11" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AA12" s="5" t="s">
+      <c r="AB11" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AB12" s="5" t="s">
+      <c r="AC11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD11" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="AC12" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="AD12" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AD12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
+  <autoFilter ref="A1:AD11" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2133,27 +2080,27 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
